--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136086962</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136087163</v>
       </c>
       <c r="B3" t="n">
-        <v>92776</v>
+        <v>92779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136087281</v>
       </c>
       <c r="B4" t="n">
-        <v>92776</v>
+        <v>92779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136087394</v>
       </c>
       <c r="B5" t="n">
-        <v>92498</v>
+        <v>92501</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136087106</v>
       </c>
       <c r="B6" t="n">
-        <v>92065</v>
+        <v>92068</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136087006</v>
       </c>
       <c r="B9" t="n">
-        <v>98770</v>
+        <v>98773</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136087064</v>
       </c>
       <c r="B10" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>136087330</v>
       </c>
       <c r="B11" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136087354</v>
       </c>
       <c r="B12" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136087518</v>
       </c>
       <c r="B13" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136087632</v>
       </c>
       <c r="B15" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136086962</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>136087163</v>
       </c>
       <c r="B3" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>136087281</v>
       </c>
       <c r="B4" t="n">
-        <v>92779</v>
+        <v>92780</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1025,7 +1025,7 @@
         <v>136087394</v>
       </c>
       <c r="B5" t="n">
-        <v>92501</v>
+        <v>92502</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>136087106</v>
       </c>
       <c r="B6" t="n">
-        <v>92068</v>
+        <v>92069</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136087006</v>
       </c>
       <c r="B9" t="n">
-        <v>98773</v>
+        <v>98774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>136087064</v>
       </c>
       <c r="B10" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
         <v>136087330</v>
       </c>
       <c r="B11" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         <v>136087354</v>
       </c>
       <c r="B12" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
         <v>136087518</v>
       </c>
       <c r="B13" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>136087632</v>
       </c>
       <c r="B15" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ15"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99346</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Stefan Björklund</t>
+          <t>Stefan Björklund, Bo Eriksson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2219,6 +2219,135 @@
       <c r="AZ15" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136087632</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>136945927</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>587096</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6647684</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sala stad</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>U-Sal-1183</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136945927</t>
         </is>
       </c>
     </row>
@@ -2238,6 +2367,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945927</v>
+        <v>136945713</v>
       </c>
       <c r="B16" t="n">
         <v>99353</v>
@@ -2252,32 +2252,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
+          <t>Gräskärret, S om (knärot 2), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587096</v>
+        <v>587029</v>
       </c>
       <c r="R16" t="n">
-        <v>6647684</v>
+        <v>6647728</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,7 +2293,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1183</t>
+          <t>U-Sal-1182</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+          <t>X: (10), A 088/962(10), egentligen (15)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,6 +2338,135 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136945713</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136945927</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99353</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587096</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sala stad</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>U-Sal-1183</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2368,6 +2489,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945713</v>
+        <v>136945927</v>
       </c>
       <c r="B16" t="n">
         <v>99353</v>
@@ -2252,24 +2252,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 2), Vstm</t>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587029</v>
+        <v>587096</v>
       </c>
       <c r="R16" t="n">
-        <v>6647728</v>
+        <v>6647684</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,7 +2301,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1182</t>
+          <t>U-Sal-1183</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>X: (10), A 088/962(10), egentligen (15)</t>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,135 +2346,6 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136945713</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136945927</v>
-      </c>
-      <c r="B17" t="n">
-        <v>99353</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>587096</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6647684</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sala stad</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>U-Sal-1183</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2489,7 +2368,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945927</v>
+        <v>136945713</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,32 +2252,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
+          <t>Gräskärret, S om (knärot 2), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587096</v>
+        <v>587029</v>
       </c>
       <c r="R16" t="n">
-        <v>6647684</v>
+        <v>6647728</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,7 +2293,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1183</t>
+          <t>U-Sal-1182</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+          <t>X: (10), A 088/962(10), egentligen (15)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,6 +2338,135 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136945713</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136945927</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99389</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587096</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sala stad</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>U-Sal-1183</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2368,6 +2489,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945713</v>
+        <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,24 +2252,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 2), Vstm</t>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587029</v>
+        <v>587096</v>
       </c>
       <c r="R16" t="n">
-        <v>6647728</v>
+        <v>6647684</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,7 +2301,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1182</t>
+          <t>U-Sal-1183</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>X: (10), A 088/962(10), egentligen (15)</t>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,135 +2346,6 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136945713</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136945927</v>
-      </c>
-      <c r="B17" t="n">
-        <v>99389</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>587096</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6647684</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sala stad</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>U-Sal-1183</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2489,7 +2368,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ16"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2224,10 +2224,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945927</v>
+        <v>136945713</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2252,32 +2252,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
+          <t>Gräskärret, S om (knärot 2), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587096</v>
+        <v>587029</v>
       </c>
       <c r="R16" t="n">
-        <v>6647684</v>
+        <v>6647728</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,7 +2293,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1183</t>
+          <t>U-Sal-1182</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2316,7 +2308,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+          <t>X: (10), A 088/962(10), egentligen (15)</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,6 +2338,135 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136945713</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>136945927</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99405</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>587096</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6647684</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sala stad</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>U-Sal-1183</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Bo Eriksson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Stefan Björklund</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2368,6 +2489,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2224,7 +2224,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136945713</v>
+        <v>136945927</v>
       </c>
       <c r="B16" t="n">
         <v>99405</v>
@@ -2252,24 +2252,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Gräskärret, S om (knärot 2), Vstm</t>
+          <t>Gräskärret, S om (knärot 3), Vstm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>587029</v>
+        <v>587096</v>
       </c>
       <c r="R16" t="n">
-        <v>6647728</v>
+        <v>6647684</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2293,7 +2301,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>U-Sal-1182</t>
+          <t>U-Sal-1183</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -2308,7 +2316,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>X: (10), A 088/962(10), egentligen (15)</t>
+          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,135 +2346,6 @@
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136945713</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>136945927</v>
-      </c>
-      <c r="B17" t="n">
-        <v>99405</v>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Gräskärret, S om (knärot 3), Vstm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>587096</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6647684</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Sala</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Västmanland</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Sala stad</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>U-Sal-1183</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>minst,X (10), 18 dm2, A: 159/937 (10) 20 dm2, B: 141/924 (10 )not</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Bo Eriksson</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Stefan Björklund</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-      <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136945927</t>
         </is>
@@ -2489,7 +2368,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 29249-2026 artfynd.xlsx
+++ b/artfynd/A 29249-2026 artfynd.xlsx
@@ -1997,7 +1997,7 @@
         <v>136087582</v>
       </c>
       <c r="B14" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>136945927</v>
       </c>
       <c r="B16" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
